--- a/data/dividends_info_20260524.xlsx
+++ b/data/dividends_info_20260524.xlsx
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>28.39999961853027</v>
+        <v>28.54999923706055</v>
       </c>
       <c r="I53" t="n">
-        <v>3.90845075672379</v>
+        <v>3.887916040849196</v>
       </c>
       <c r="J53" t="n">
         <v>11</v>
@@ -10178,129 +10178,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Estrima S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Industrie De Nora S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Italgas S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Officina Stellare S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Portobello S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Telesia S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>